--- a/25-26/Invoices 25-26/37 BK037 December 25-26 KIEN CUONG TRADING (Anh Doan) Galaxy Black Short hand polish (RJSL) (B)/Invoice template,PO, Packing List.xlsx
+++ b/25-26/Invoices 25-26/37 BK037 December 25-26 KIEN CUONG TRADING (Anh Doan) Galaxy Black Short hand polish (RJSL) (B)/Invoice template,PO, Packing List.xlsx
@@ -5,21 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\B K EXPORTS\BK Exports bills\25-26\Invoices 25-26\37 BK037 December 25-26 KIEN CUONG TRADING (VK)(Anh Doan) Galaxy Black Short hand polish (RJSL)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\B K EXPORTS\BK Exports bills\25-26\Invoices 25-26\37 BK037 December 25-26 KIEN CUONG TRADING (Anh Doan) Galaxy Black Short hand polish (RJSL) (B)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7245" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7245" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="company data" sheetId="1" r:id="rId1"/>
     <sheet name="input data" sheetId="2" r:id="rId2"/>
     <sheet name="Invoice" sheetId="3" r:id="rId3"/>
-    <sheet name="Peacking List" sheetId="4" r:id="rId4"/>
-    <sheet name="PO" sheetId="5" r:id="rId5"/>
+    <sheet name="CN" sheetId="6" r:id="rId4"/>
+    <sheet name="Peacking List" sheetId="4" r:id="rId5"/>
+    <sheet name="PO" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">PO!$A$1:$K$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">PO!$A$1:$K$42</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="175">
   <si>
     <t>financial year</t>
   </si>
@@ -643,6 +644,21 @@
 Contact: 0983037116
 Email: Custom.kc68@gmail.com </t>
   </si>
+  <si>
+    <t>CREDIT NOTE</t>
+  </si>
+  <si>
+    <t>CR NO.</t>
+  </si>
+  <si>
+    <t>BK003/25-26</t>
+  </si>
+  <si>
+    <t>One Hundred Dollars</t>
+  </si>
+  <si>
+    <t>Invoice number: BK037/25-26.DISCOUNT FOR DEFECT</t>
+  </si>
 </sst>
 </file>
 
@@ -831,7 +847,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -1224,11 +1240,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="196">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1663,6 +1692,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1764,6 +1811,61 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>243470</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>77302</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B73B709-7356-421F-9217-A99C699D1311}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3824870" y="7267575"/>
+          <a:ext cx="1861555" cy="763102"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>269263</xdr:colOff>
       <xdr:row>38</xdr:row>
@@ -1815,7 +1917,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -33042,6 +33144,705 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="114" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="86"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="100" t="s">
+        <v>171</v>
+      </c>
+      <c r="F3" s="90"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="100" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="90"/>
+      <c r="J3" s="91"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="115" t="s">
+        <v>172</v>
+      </c>
+      <c r="F4" s="86"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="116">
+        <v>46065</v>
+      </c>
+      <c r="I4" s="117"/>
+      <c r="J4" s="118"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="100" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="90"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="100" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" s="90"/>
+      <c r="J5" s="91"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="85"/>
+      <c r="H6" s="119" t="str">
+        <f>'input data'!B5</f>
+        <v>AD2403250650768</v>
+      </c>
+      <c r="I6" s="86"/>
+      <c r="J6" s="85"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="100" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="90"/>
+      <c r="G7" s="91"/>
+      <c r="H7" s="100" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="90"/>
+      <c r="J7" s="91"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="94" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="86"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="84" t="s">
+        <v>51</v>
+      </c>
+      <c r="I8" s="86"/>
+      <c r="J8" s="85"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="100" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="90"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="100" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="90"/>
+      <c r="J9" s="91"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="104" t="str">
+        <f>'input data'!B14</f>
+        <v>Loose packing</v>
+      </c>
+      <c r="F10" s="82"/>
+      <c r="G10" s="93"/>
+      <c r="H10" s="104" t="str">
+        <f>'input data'!B13 &amp; " " &amp; 'input data'!B15</f>
+        <v>1 FCL</v>
+      </c>
+      <c r="I10" s="82"/>
+      <c r="J10" s="93"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="108" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="90"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="125" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="98"/>
+      <c r="G11" s="99"/>
+      <c r="H11" s="120" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="98"/>
+      <c r="J11" s="99"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="123" t="str">
+        <f>'input data'!B6</f>
+        <v>To the Order</v>
+      </c>
+      <c r="B12" s="82"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="124" t="str">
+        <f>'input data'!B16</f>
+        <v>CNF</v>
+      </c>
+      <c r="F12" s="82"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="121" t="str">
+        <f>'input data'!B17</f>
+        <v>100% Against Documents</v>
+      </c>
+      <c r="I12" s="82"/>
+      <c r="J12" s="93"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="19"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="85"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="85"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="122" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="90"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="90"/>
+      <c r="I14" s="90"/>
+      <c r="J14" s="91"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="126" t="str">
+        <f>'input data'!B7</f>
+        <v xml:space="preserve">KIEN CUONG TRADING, PRODUCTION AND IMPORT-EXPORT JOINT STOCK COMPANY
+Address: No. 55 An Duong Vuong Street, Phuc Cuong Quarter, Quang Phu Ward, Thanh Hoa Province, Vietnam
+Tax ID: 2803014691
+Contact: 0983037116
+Email: Custom.kc68@gmail.com </v>
+      </c>
+      <c r="B15" s="82"/>
+      <c r="C15" s="82"/>
+      <c r="D15" s="93"/>
+      <c r="E15" s="92"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="93"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="92"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="92"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="82"/>
+      <c r="I16" s="82"/>
+      <c r="J16" s="93"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="92"/>
+      <c r="B17" s="82"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="92"/>
+      <c r="F17" s="82"/>
+      <c r="G17" s="82"/>
+      <c r="H17" s="82"/>
+      <c r="I17" s="82"/>
+      <c r="J17" s="93"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="92"/>
+      <c r="B18" s="82"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="93"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="82"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="82"/>
+      <c r="J18" s="93"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="92"/>
+      <c r="B19" s="82"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="93"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="82"/>
+      <c r="G19" s="82"/>
+      <c r="H19" s="82"/>
+      <c r="I19" s="82"/>
+      <c r="J19" s="93"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="96"/>
+      <c r="B20" s="86"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="96"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="86"/>
+      <c r="J20" s="85"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="127" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="91"/>
+      <c r="C21" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="91"/>
+      <c r="E21" s="127" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="90"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="90"/>
+      <c r="J21" s="91"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="128" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" s="93"/>
+      <c r="C22" s="130" t="str">
+        <f>'input data'!B19</f>
+        <v>CHENNAI</v>
+      </c>
+      <c r="D22" s="93"/>
+      <c r="E22" s="131" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="82"/>
+      <c r="G22" s="93"/>
+      <c r="H22" s="131" t="str">
+        <f>'input data'!B23</f>
+        <v>VIETNAM</v>
+      </c>
+      <c r="I22" s="82"/>
+      <c r="J22" s="93"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="132"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="96"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="96"/>
+      <c r="F23" s="86"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="96"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="85"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="100" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="91"/>
+      <c r="C24" s="129" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="91"/>
+      <c r="E24" s="100" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="90"/>
+      <c r="G24" s="91"/>
+      <c r="H24" s="129" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="90"/>
+      <c r="J24" s="91"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="94"/>
+      <c r="B25" s="85"/>
+      <c r="C25" s="84" t="str">
+        <f>'input data'!B20</f>
+        <v>CHENNAI</v>
+      </c>
+      <c r="D25" s="85"/>
+      <c r="E25" s="84" t="str">
+        <f>'input data'!B21</f>
+        <v>HAI PHONG</v>
+      </c>
+      <c r="F25" s="86"/>
+      <c r="G25" s="85"/>
+      <c r="H25" s="84" t="str">
+        <f>'input data'!B22</f>
+        <v>HAI PHONG</v>
+      </c>
+      <c r="I25" s="86"/>
+      <c r="J25" s="85"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="87" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="89" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="190"/>
+      <c r="D26" s="190"/>
+      <c r="E26" s="190"/>
+      <c r="F26" s="190"/>
+      <c r="G26" s="191"/>
+      <c r="H26" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="I26" s="100" t="s">
+        <v>70</v>
+      </c>
+      <c r="J26" s="91"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="88"/>
+      <c r="B27" s="192"/>
+      <c r="C27" s="193"/>
+      <c r="D27" s="193"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="193"/>
+      <c r="G27" s="194"/>
+      <c r="H27" s="76" t="s">
+        <v>71</v>
+      </c>
+      <c r="I27" s="84" t="s">
+        <v>72</v>
+      </c>
+      <c r="J27" s="85"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="27">
+        <v>1</v>
+      </c>
+      <c r="B28" s="155" t="s">
+        <v>174</v>
+      </c>
+      <c r="C28" s="181"/>
+      <c r="D28" s="181"/>
+      <c r="E28" s="181"/>
+      <c r="F28" s="181"/>
+      <c r="G28" s="195"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="111">
+        <v>100</v>
+      </c>
+      <c r="J28" s="99"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="112" t="s">
+        <v>151</v>
+      </c>
+      <c r="I29" s="69"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="104" t="str">
+        <f>UPPER('input data'!B24)</f>
+        <v>CSLU2019899</v>
+      </c>
+      <c r="B30" s="82"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="112"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="20"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="19"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="102"/>
+      <c r="G31" s="103"/>
+      <c r="H31" s="112"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="20"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="30"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="113"/>
+      <c r="I32" s="109"/>
+      <c r="J32" s="110"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="107">
+        <f>SUM(I28:J32)</f>
+        <v>100</v>
+      </c>
+      <c r="J33" s="91"/>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="96"/>
+      <c r="J34" s="85"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="105" t="s">
+        <v>78</v>
+      </c>
+      <c r="B35" s="90"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="91"/>
+      <c r="E35" s="108" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="90"/>
+      <c r="G35" s="90"/>
+      <c r="H35" s="90"/>
+      <c r="I35" s="90"/>
+      <c r="J35" s="91"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="106" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" s="82"/>
+      <c r="C36" s="82"/>
+      <c r="D36" s="93"/>
+      <c r="E36" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="20"/>
+    </row>
+    <row r="37" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="92"/>
+      <c r="B37" s="82"/>
+      <c r="C37" s="82"/>
+      <c r="D37" s="93"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="20"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="95" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="82"/>
+      <c r="C38" s="82"/>
+      <c r="D38" s="93"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="20"/>
+    </row>
+    <row r="39" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="96"/>
+      <c r="B39" s="86"/>
+      <c r="C39" s="86"/>
+      <c r="D39" s="85"/>
+      <c r="E39" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="57">
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="B26:G27"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E12:G13"/>
+    <mergeCell ref="H12:J13"/>
+    <mergeCell ref="E14:J20"/>
+    <mergeCell ref="A15:D20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D23"/>
+    <mergeCell ref="E22:G23"/>
+    <mergeCell ref="H22:J23"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="H29:H32"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I33:J34"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="E35:J35"/>
+    <mergeCell ref="A36:D37"/>
+    <mergeCell ref="A38:D39"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A9" r:id="rId1"/>
+    <hyperlink ref="A10" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="98" orientation="portrait" r:id="rId3"/>
+  <drawing r:id="rId4"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J998"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -34725,7 +35526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y997"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
